--- a/results/count/543_3/measurements.xlsx
+++ b/results/count/543_3/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,189 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v2-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1789.5455</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D6" t="n">
+        <v>797.487</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>major_axis_length</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>67.7925</v>
+      </c>
+      <c r="C7" t="n">
+        <v>69.2617</v>
+      </c>
+      <c r="D7" t="n">
+        <v>19.0959</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>minor_axis_length</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>35.2772</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.2244</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1039</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.9772</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.9305</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8264</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8554</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9295</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>11</v>
       </c>
     </row>

--- a/results/count/543_3/measurements.xlsx
+++ b/results/count/543_3/measurements.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1789.5455</v>
+        <v>2187.2222</v>
       </c>
       <c r="C6" t="n">
-        <v>1883</v>
+        <v>2174</v>
       </c>
       <c r="D6" t="n">
-        <v>797.487</v>
+        <v>598.7996000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.7925</v>
+        <v>82.3704</v>
       </c>
       <c r="C7" t="n">
-        <v>69.2617</v>
+        <v>87.6934</v>
       </c>
       <c r="D7" t="n">
-        <v>19.0959</v>
+        <v>10.0353</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.2772</v>
+        <v>36.7931</v>
       </c>
       <c r="C8" t="n">
-        <v>35.2244</v>
+        <v>35.2412</v>
       </c>
       <c r="D8" t="n">
-        <v>11.1039</v>
+        <v>11.1805</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9772</v>
+        <v>2.387</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9305</v>
+        <v>2.2947</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4898</v>
+        <v>0.6949</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8264</v>
+        <v>0.8811</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8554</v>
+        <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1113</v>
+        <v>0.0775</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8989</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="C11" t="n">
         <v>0.9295</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0798</v>
+        <v>0.0959</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,31 +919,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>722</v>
+        <v>1344</v>
       </c>
       <c r="C7" t="n">
-        <v>43.2702</v>
+        <v>87.6934</v>
       </c>
       <c r="D7" t="n">
-        <v>22.414</v>
+        <v>23.0299</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9305</v>
+        <v>3.8078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8554</v>
+        <v>0.9649</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8741</v>
+        <v>0.7764</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4699</v>
+        <v>0.2206</v>
       </c>
       <c r="I7" t="n">
-        <v>527.5942</v>
+        <v>545.1897</v>
       </c>
       <c r="J7" t="n">
-        <v>873.4211</v>
+        <v>876.8661</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -959,31 +959,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>622</v>
+        <v>1683</v>
       </c>
       <c r="C8" t="n">
-        <v>40.6141</v>
+        <v>71.0123</v>
       </c>
       <c r="D8" t="n">
-        <v>21.3497</v>
+        <v>31.3735</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9023</v>
+        <v>2.2634</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8507</v>
+        <v>0.8971</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8724</v>
+        <v>0.9355</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1962</v>
+        <v>-0.0518</v>
       </c>
       <c r="I8" t="n">
-        <v>565.6141</v>
+        <v>634.6803</v>
       </c>
       <c r="J8" t="n">
-        <v>880.865</v>
+        <v>198.3155</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -999,31 +999,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1683</v>
+        <v>2203</v>
       </c>
       <c r="C9" t="n">
-        <v>71.0123</v>
+        <v>91.2092</v>
       </c>
       <c r="D9" t="n">
-        <v>31.3735</v>
+        <v>31.4053</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2634</v>
+        <v>2.9043</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8971</v>
+        <v>0.9389</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9355</v>
+        <v>0.9295</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0518</v>
+        <v>0.0832</v>
       </c>
       <c r="I9" t="n">
-        <v>634.6803</v>
+        <v>734.3013999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>198.3155</v>
+        <v>635.4403</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1039,31 +1039,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2203</v>
+        <v>2633</v>
       </c>
       <c r="C10" t="n">
-        <v>91.2092</v>
+        <v>93.5592</v>
       </c>
       <c r="D10" t="n">
-        <v>31.4053</v>
+        <v>36.2778</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9043</v>
+        <v>2.579</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9389</v>
+        <v>0.9218</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9295</v>
+        <v>0.9454</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0832</v>
+        <v>0.0457</v>
       </c>
       <c r="I10" t="n">
-        <v>734.3013999999999</v>
+        <v>780.5761</v>
       </c>
       <c r="J10" t="n">
-        <v>635.4403</v>
+        <v>481.4953</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1079,116 +1079,36 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1199</v>
+        <v>531</v>
       </c>
       <c r="C11" t="n">
-        <v>44.7166</v>
+        <v>28.7881</v>
       </c>
       <c r="D11" t="n">
-        <v>37.2309</v>
+        <v>24.8252</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2011</v>
+        <v>1.1596</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5063</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9508</v>
+        <v>0.9332</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2104</v>
+        <v>0.5942</v>
       </c>
       <c r="I11" t="n">
-        <v>759.2694</v>
+        <v>1012.2844</v>
       </c>
       <c r="J11" t="n">
-        <v>480.779</v>
+        <v>184.8343</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1434</v>
-      </c>
-      <c r="C12" t="n">
-        <v>57.0359</v>
-      </c>
-      <c r="D12" t="n">
-        <v>35.2244</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.6192</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.7865</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.9416</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>798.3912</v>
-      </c>
-      <c r="J12" t="n">
-        <v>482.0941</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>531</v>
-      </c>
-      <c r="C13" t="n">
-        <v>28.7881</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24.8252</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.1596</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5063</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.9332</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1012.2844</v>
-      </c>
-      <c r="J13" t="n">
-        <v>184.8343</v>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>px</t>
         </is>
